--- a/artfynd/A 21436-2026 artfynd.xlsx
+++ b/artfynd/A 21436-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>101554965</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613366.458181057</v>
+        <v>613367</v>
       </c>
       <c r="R2" t="n">
-        <v>6967181.126153192</v>
+        <v>6967181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,16 +783,11 @@
         <v>101554978</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613337.9560525012</v>
+        <v>613338</v>
       </c>
       <c r="R3" t="n">
-        <v>6967236.878848222</v>
+        <v>6967237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2022-06-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +888,7 @@
         <v>101554973</v>
       </c>
       <c r="B4" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613358.1249642358</v>
+        <v>613358</v>
       </c>
       <c r="R4" t="n">
-        <v>6967210.122190082</v>
+        <v>6967210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +956,9 @@
           <t>2022-06-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 21436-2026 artfynd.xlsx
+++ b/artfynd/A 21436-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>